--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУБЛС/КСУБЛС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,49 +55,55 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1918 O5 Търговище</t>
-  </si>
-  <si>
-    <t>1193 Казанлък</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>АМ Тракия 243км , посока София</t>
+  </si>
+  <si>
+    <t>Пазарджик</t>
+  </si>
+  <si>
+    <t>Нова Загора</t>
   </si>
   <si>
     <t>В8986ВР</t>
   </si>
   <si>
+    <t>В9053ВТ</t>
+  </si>
+  <si>
     <t>78970155027720873</t>
   </si>
   <si>
+    <t>78970155027720881</t>
+  </si>
+  <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>07:53:00</t>
-  </si>
-  <si>
-    <t>09:37:00</t>
-  </si>
-  <si>
-    <t>10:01:00</t>
-  </si>
-  <si>
-    <t>13:40:00</t>
-  </si>
-  <si>
-    <t>3236592608 3236592608</t>
-  </si>
-  <si>
-    <t>3236598375 3236598375</t>
-  </si>
-  <si>
-    <t>3236663062 3236663062</t>
-  </si>
-  <si>
-    <t>3236665115 3236665115</t>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>07:58</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>14:07</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУБЛС</t>
@@ -523,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -532,17 +535,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,145 +584,133 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>15.42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
+        <v>20.03</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.59</v>
       </c>
       <c r="H2" s="1">
-        <v>0.65</v>
+        <v>31.848</v>
       </c>
       <c r="I2" s="1">
-        <v>10.023</v>
+        <v>1.62</v>
       </c>
       <c r="J2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>10.177</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
+        <v>32.449</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>172587</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>11.61</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
+        <v>32.28</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.66</v>
       </c>
       <c r="H3" s="1">
-        <v>0.65</v>
+        <v>21.305</v>
       </c>
       <c r="I3" s="1">
-        <v>7.546</v>
+        <v>0.67</v>
       </c>
       <c r="J3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>7.663</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
+        <v>21.628</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>172588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46254</v>
+        <v>46275</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>17.23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
+        <v>20.63</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.66</v>
       </c>
       <c r="H4" s="1">
-        <v>0.65</v>
+        <v>13.616</v>
       </c>
       <c r="I4" s="1">
-        <v>11.2</v>
+        <v>0.67</v>
       </c>
       <c r="J4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
-        <v>11.372</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
+        <v>13.822</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>277532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -729,110 +719,229 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>25.82</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H5" s="1">
+        <v>17.041</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J5" s="1">
+        <v>17.299</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>240617</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>15.82</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10.441</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10.599</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>127355</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>15.7</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>10.205</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>24.33</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.89</v>
+      </c>
+      <c r="H7" s="1">
+        <v>45.984</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="J7" s="1">
+        <v>46.714</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>174607</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="7">
+        <v>94.55</v>
+      </c>
+      <c r="C12" s="8">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9">
         <v>0.66</v>
       </c>
-      <c r="K5" s="1">
-        <v>10.362</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>59.96</v>
-      </c>
-      <c r="C10" s="8">
-        <v>4</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0.65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>38.97</v>
-      </c>
-      <c r="F10" s="7">
-        <v>39.57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="11">
-        <v>59.96</v>
-      </c>
-      <c r="C11" s="12">
-        <v>4</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="11">
-        <v>38.97</v>
-      </c>
-      <c r="F11" s="11">
-        <v>39.57</v>
+      <c r="E12" s="7">
+        <v>62.4</v>
+      </c>
+      <c r="F12" s="7">
+        <v>63.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7">
+        <v>24.33</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1.89001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>45.98</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7">
+        <v>20.03</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1.59001</v>
+      </c>
+      <c r="E14" s="7">
+        <v>31.85</v>
+      </c>
+      <c r="F14" s="7">
+        <v>32.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="11">
+        <v>138.91</v>
+      </c>
+      <c r="C15" s="12">
+        <v>6</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="11">
+        <v>140.23</v>
+      </c>
+      <c r="F15" s="11">
+        <v>142.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
